--- a/2023-08 A小区1单元.xlsx
+++ b/2023-08 A小区1单元.xlsx
@@ -4,17 +4,33 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12525"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="130">
+  <si>
+    <t>备注信息</t>
+  </si>
   <si>
     <t>计费号</t>
   </si>
@@ -34,10 +50,10 @@
     <t>录入月份</t>
   </si>
   <si>
-    <t>2023-04</t>
-  </si>
-  <si>
     <t>2023-06</t>
+  </si>
+  <si>
+    <t>无</t>
   </si>
   <si>
     <t>442667</t>
@@ -406,7 +422,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -421,11 +437,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -579,7 +595,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -588,12 +604,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -779,64 +789,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -963,7 +921,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -975,152 +933,124 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1440,19 +1370,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75"/>
-  <cols>
-    <col min="1" max="1" width="11.5714285714286" customWidth="1"/>
-    <col min="2" max="2" width="8.14285714285714" customWidth="1"/>
-    <col min="3" max="3" width="10.8571428571429" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="1.07619047619048" customWidth="1"/>
-    <col min="6" max="6" width="13.7142857142857" customWidth="1"/>
-    <col min="7" max="7" width="5.42857142857143" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" outlineLevelCol="7"/>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:10">
+    <row r="1" ht="14.25" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1462,898 +1383,813 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="4"/>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25" spans="1:8">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1">
+        <v>17</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="1">
+        <v>5</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="1">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="1">
+        <v>25</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="1">
+        <v>23</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="1">
+        <v>15</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="1">
+        <v>27</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="1">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" spans="1:8">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="1">
+        <v>22</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" spans="1:8">
+      <c r="A12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="1">
+        <v>21</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" spans="1:8">
+      <c r="A13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="1">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" spans="1:8">
+      <c r="A14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="1">
+        <v>21</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" spans="1:8">
+      <c r="A15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="1">
+        <v>6</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" spans="1:8">
+      <c r="A16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="1">
+        <v>6</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" spans="1:8">
+      <c r="A17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="1">
+        <v>24</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" spans="1:8">
+      <c r="A18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="1">
+        <v>14</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" spans="1:8">
+      <c r="A19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" s="1">
+        <v>7</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="1">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+    </row>
+    <row r="20" ht="14.25" spans="1:8">
+      <c r="A20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="1">
+        <v>12</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" spans="1:8">
+      <c r="A21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" s="1">
+        <v>6</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" spans="1:8">
+      <c r="A22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" s="1">
+        <v>14</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" spans="1:8">
+      <c r="A23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F23" s="1">
+        <v>8</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="1">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="24" ht="14.25" spans="1:8">
+      <c r="A24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="1">
+        <v>11</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" spans="1:8">
+      <c r="A25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" s="1">
+        <v>28</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" spans="1:8">
+      <c r="A26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F26" s="1">
+        <v>13</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" spans="1:8">
+      <c r="A27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" s="1">
+        <v>16</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25" spans="1:8">
+      <c r="A28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F28" s="1">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" spans="1:8">
+      <c r="A29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F29" s="1">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" spans="1:8">
+      <c r="A30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F30" s="1">
+        <v>9</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="1">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="31" ht="14.25" spans="1:8">
+      <c r="A31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F31" s="1">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="1">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:10">
-      <c r="A2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="10">
-        <v>22</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="10">
-        <v>12</v>
-      </c>
-      <c r="J2" s="10">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:10">
-      <c r="A3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="10">
-        <v>27</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="10">
-        <v>10</v>
-      </c>
-      <c r="J3" s="10">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="10">
-        <v>19</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="10">
-        <v>0</v>
-      </c>
-      <c r="J4" s="10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:10">
-      <c r="A5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="10">
-        <v>33</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="10">
-        <v>8</v>
-      </c>
-      <c r="J5" s="10">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:10">
-      <c r="A6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="10">
-        <v>30</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="10">
-        <v>20</v>
-      </c>
-      <c r="J6" s="10">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:10">
-      <c r="A7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="10">
-        <v>28</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="10">
-        <v>18</v>
-      </c>
-      <c r="J7" s="10">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:10">
-      <c r="A8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="10">
-        <v>20</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="10">
-        <v>10</v>
-      </c>
-      <c r="J8" s="10">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:10">
-      <c r="A9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="10">
-        <v>32</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I9" s="10">
-        <v>22</v>
-      </c>
-      <c r="J9" s="10">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:10">
-      <c r="A10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10">
-        <v>15</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="10">
-        <v>5</v>
-      </c>
-      <c r="J10" s="10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:10">
-      <c r="A11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10">
-        <v>27</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="10">
-        <v>17</v>
-      </c>
-      <c r="J11" s="10">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:10">
-      <c r="A12" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10">
-        <v>26</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" s="10">
-        <v>16</v>
-      </c>
-      <c r="J12" s="10">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:10">
-      <c r="A13" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="10">
-        <v>13</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I13" s="10">
-        <v>3</v>
-      </c>
-      <c r="J13" s="10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:10">
-      <c r="A14" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="10">
-        <v>26</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" s="10">
-        <v>16</v>
-      </c>
-      <c r="J14" s="10">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:10">
-      <c r="A15" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="10">
-        <v>11</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I15" s="10">
-        <v>1</v>
-      </c>
-      <c r="J15" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:10">
-      <c r="A16" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="10">
-        <v>11</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I16" s="10">
-        <v>1</v>
-      </c>
-      <c r="J16" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:10">
-      <c r="A17" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="10">
-        <v>29</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I17" s="10">
-        <v>19</v>
-      </c>
-      <c r="J17" s="10">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:10">
-      <c r="A18" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="10">
-        <v>19</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I18" s="10">
-        <v>9</v>
-      </c>
-      <c r="J18" s="10">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:10">
-      <c r="A19" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="10">
-        <v>12</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I19" s="10">
-        <v>2</v>
-      </c>
-      <c r="J19" s="10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:10">
-      <c r="A20" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="10">
-        <v>17</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I20" s="10">
-        <v>7</v>
-      </c>
-      <c r="J20" s="10">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:10">
-      <c r="A21" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="10">
-        <v>11</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I21" s="10">
-        <v>1</v>
-      </c>
-      <c r="J21" s="10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:10">
-      <c r="A22" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="10">
-        <v>19</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I22" s="10">
-        <v>9</v>
-      </c>
-      <c r="J22" s="10">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:10">
-      <c r="A23" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="10">
-        <v>13</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I23" s="10">
-        <v>3</v>
-      </c>
-      <c r="J23" s="10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:10">
-      <c r="A24" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="10">
-        <v>16</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I24" s="10">
-        <v>6</v>
-      </c>
-      <c r="J24" s="10">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:10">
-      <c r="A25" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="10">
-        <v>33</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I25" s="10">
-        <v>23</v>
-      </c>
-      <c r="J25" s="10">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" spans="1:10">
-      <c r="A26" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="10">
-        <v>18</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I26" s="10">
-        <v>8</v>
-      </c>
-      <c r="J26" s="10">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" spans="1:10">
-      <c r="A27" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="10">
-        <v>21</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I27" s="10">
-        <v>11</v>
-      </c>
-      <c r="J27" s="10">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" spans="1:10">
-      <c r="A28" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="10">
-        <v>15</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I28" s="10">
-        <v>5</v>
-      </c>
-      <c r="J28" s="10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" spans="1:10">
-      <c r="A29" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="10">
-        <v>15</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I29" s="10">
-        <v>5</v>
-      </c>
-      <c r="J29" s="10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" ht="16.5" spans="1:10">
-      <c r="A30" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="10">
-        <v>14</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I30" s="10">
-        <v>4</v>
-      </c>
-      <c r="J30" s="10">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" spans="1:10">
-      <c r="A31" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="10">
-        <v>15</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I31" s="10">
-        <v>5</v>
-      </c>
-      <c r="J31" s="10">
-        <v>10</v>
-      </c>
+    <row r="32" ht="14.25" spans="1:8">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-  </mergeCells>
   <pageMargins left="0.3937008" right="0.3937008" top="0.3937008" bottom="0.3937008" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" useFirstPageNumber="1"/>
   <headerFooter/>
